--- a/fantasy_app.xlsx
+++ b/fantasy_app.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alank\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alank\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC467408-CA3E-4FDB-91BF-D1A3EF3D1CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEB0F59-A696-48A2-B55C-DFDB3CC80862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{95FEA008-BA97-43C4-8284-3C0514AFD86D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3233" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2467" uniqueCount="357">
   <si>
     <t>Pass Yds</t>
   </si>
@@ -1481,7 +1481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB547F50-6C6F-4210-B1EE-78B38AE722A6}">
-  <dimension ref="A1:P138"/>
+  <dimension ref="A1:P123"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1559,20 +1559,20 @@
       <c r="I2">
         <v>4</v>
       </c>
-      <c r="J2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K2" t="s">
-        <v>300</v>
-      </c>
-      <c r="L2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M2" t="s">
-        <v>300</v>
-      </c>
-      <c r="N2" t="s">
-        <v>300</v>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -1606,8 +1606,8 @@
       <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
-        <v>300</v>
+      <c r="J3">
+        <v>0</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -1615,11 +1615,11 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3" t="s">
-        <v>300</v>
-      </c>
-      <c r="N3" t="s">
-        <v>300</v>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -1653,26 +1653,26 @@
       <c r="I4">
         <v>6</v>
       </c>
-      <c r="J4" t="s">
-        <v>300</v>
-      </c>
-      <c r="K4" t="s">
-        <v>300</v>
-      </c>
-      <c r="L4" t="s">
-        <v>300</v>
-      </c>
-      <c r="M4" t="s">
-        <v>300</v>
-      </c>
-      <c r="N4" t="s">
-        <v>300</v>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
-      <c r="P4" t="s">
-        <v>300</v>
+      <c r="P4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1700,23 +1700,23 @@
       <c r="I5">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
-        <v>300</v>
-      </c>
-      <c r="K5" t="s">
-        <v>300</v>
-      </c>
-      <c r="L5" t="s">
-        <v>300</v>
-      </c>
-      <c r="M5" t="s">
-        <v>300</v>
-      </c>
-      <c r="N5" t="s">
-        <v>300</v>
-      </c>
-      <c r="O5" t="s">
-        <v>300</v>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
       </c>
       <c r="P5">
         <v>5</v>
@@ -1747,23 +1747,23 @@
       <c r="I6">
         <v>2</v>
       </c>
-      <c r="J6" t="s">
-        <v>300</v>
-      </c>
-      <c r="K6" t="s">
-        <v>300</v>
-      </c>
-      <c r="L6" t="s">
-        <v>300</v>
-      </c>
-      <c r="M6" t="s">
-        <v>300</v>
-      </c>
-      <c r="N6" t="s">
-        <v>300</v>
-      </c>
-      <c r="O6" t="s">
-        <v>300</v>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
       </c>
       <c r="P6">
         <v>5</v>
@@ -1800,20 +1800,20 @@
       <c r="K7">
         <v>2</v>
       </c>
-      <c r="L7" t="s">
-        <v>300</v>
-      </c>
-      <c r="M7" t="s">
-        <v>300</v>
-      </c>
-      <c r="N7" t="s">
-        <v>300</v>
-      </c>
-      <c r="O7" t="s">
-        <v>300</v>
-      </c>
-      <c r="P7" t="s">
-        <v>300</v>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1841,20 +1841,20 @@
       <c r="I8">
         <v>3</v>
       </c>
-      <c r="J8" t="s">
-        <v>300</v>
-      </c>
-      <c r="K8" t="s">
-        <v>300</v>
-      </c>
-      <c r="L8" t="s">
-        <v>300</v>
-      </c>
-      <c r="M8" t="s">
-        <v>300</v>
-      </c>
-      <c r="N8" t="s">
-        <v>300</v>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -1888,23 +1888,23 @@
       <c r="I9">
         <v>5</v>
       </c>
-      <c r="J9" t="s">
-        <v>300</v>
-      </c>
-      <c r="K9" t="s">
-        <v>300</v>
-      </c>
-      <c r="L9" t="s">
-        <v>300</v>
-      </c>
-      <c r="M9" t="s">
-        <v>300</v>
-      </c>
-      <c r="N9" t="s">
-        <v>300</v>
-      </c>
-      <c r="O9" t="s">
-        <v>300</v>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1944,17 +1944,17 @@
       <c r="L10">
         <v>1</v>
       </c>
-      <c r="M10" t="s">
-        <v>300</v>
-      </c>
-      <c r="N10" t="s">
-        <v>300</v>
-      </c>
-      <c r="O10" t="s">
-        <v>300</v>
-      </c>
-      <c r="P10" t="s">
-        <v>300</v>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1982,20 +1982,20 @@
       <c r="I11">
         <v>5</v>
       </c>
-      <c r="J11" t="s">
-        <v>300</v>
-      </c>
-      <c r="K11" t="s">
-        <v>300</v>
-      </c>
-      <c r="L11" t="s">
-        <v>300</v>
-      </c>
-      <c r="M11" t="s">
-        <v>300</v>
-      </c>
-      <c r="N11" t="s">
-        <v>300</v>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
       </c>
       <c r="O11">
         <v>1</v>
@@ -2026,8 +2026,8 @@
       <c r="H12">
         <v>56</v>
       </c>
-      <c r="I12" t="s">
-        <v>300</v>
+      <c r="I12">
+        <v>0</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2038,17 +2038,17 @@
       <c r="L12">
         <v>1</v>
       </c>
-      <c r="M12" t="s">
-        <v>300</v>
-      </c>
-      <c r="N12" t="s">
-        <v>300</v>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
-      <c r="P12" t="s">
-        <v>300</v>
+      <c r="P12">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -2076,23 +2076,23 @@
       <c r="I13">
         <v>5</v>
       </c>
-      <c r="J13" t="s">
-        <v>300</v>
-      </c>
-      <c r="K13" t="s">
-        <v>300</v>
-      </c>
-      <c r="L13" t="s">
-        <v>300</v>
-      </c>
-      <c r="M13" t="s">
-        <v>300</v>
-      </c>
-      <c r="N13" t="s">
-        <v>300</v>
-      </c>
-      <c r="O13" t="s">
-        <v>300</v>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
       </c>
       <c r="P13">
         <v>3</v>
@@ -2120,23 +2120,23 @@
       <c r="H14">
         <v>489</v>
       </c>
-      <c r="I14" t="s">
-        <v>300</v>
-      </c>
-      <c r="J14" t="s">
-        <v>300</v>
-      </c>
-      <c r="K14" t="s">
-        <v>300</v>
-      </c>
-      <c r="L14" t="s">
-        <v>300</v>
-      </c>
-      <c r="M14" t="s">
-        <v>300</v>
-      </c>
-      <c r="N14" t="s">
-        <v>300</v>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
       </c>
       <c r="O14">
         <v>3</v>
@@ -2170,23 +2170,23 @@
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15" t="s">
-        <v>300</v>
-      </c>
-      <c r="K15" t="s">
-        <v>300</v>
-      </c>
-      <c r="L15" t="s">
-        <v>300</v>
-      </c>
-      <c r="M15" t="s">
-        <v>300</v>
-      </c>
-      <c r="N15" t="s">
-        <v>300</v>
-      </c>
-      <c r="O15" t="s">
-        <v>300</v>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -2217,20 +2217,20 @@
       <c r="I16">
         <v>2</v>
       </c>
-      <c r="J16" t="s">
-        <v>300</v>
-      </c>
-      <c r="K16" t="s">
-        <v>300</v>
-      </c>
-      <c r="L16" t="s">
-        <v>300</v>
-      </c>
-      <c r="M16" t="s">
-        <v>300</v>
-      </c>
-      <c r="N16" t="s">
-        <v>300</v>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
       </c>
       <c r="O16">
         <v>3</v>
@@ -2261,26 +2261,26 @@
       <c r="H17">
         <v>233</v>
       </c>
-      <c r="I17" t="s">
-        <v>300</v>
-      </c>
-      <c r="J17" t="s">
-        <v>300</v>
-      </c>
-      <c r="K17" t="s">
-        <v>300</v>
-      </c>
-      <c r="L17" t="s">
-        <v>300</v>
-      </c>
-      <c r="M17" t="s">
-        <v>300</v>
-      </c>
-      <c r="N17" t="s">
-        <v>300</v>
-      </c>
-      <c r="O17" t="s">
-        <v>300</v>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -2311,26 +2311,26 @@
       <c r="I18">
         <v>1</v>
       </c>
-      <c r="J18" t="s">
-        <v>300</v>
-      </c>
-      <c r="K18" t="s">
-        <v>300</v>
-      </c>
-      <c r="L18" t="s">
-        <v>300</v>
-      </c>
-      <c r="M18" t="s">
-        <v>300</v>
-      </c>
-      <c r="N18" t="s">
-        <v>300</v>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
       </c>
       <c r="O18">
         <v>3</v>
       </c>
-      <c r="P18" t="s">
-        <v>300</v>
+      <c r="P18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2358,20 +2358,20 @@
       <c r="I19">
         <v>2</v>
       </c>
-      <c r="J19" t="s">
-        <v>300</v>
-      </c>
-      <c r="K19" t="s">
-        <v>300</v>
-      </c>
-      <c r="L19" t="s">
-        <v>300</v>
-      </c>
-      <c r="M19" t="s">
-        <v>300</v>
-      </c>
-      <c r="N19" t="s">
-        <v>300</v>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
       </c>
       <c r="O19">
         <v>2</v>
@@ -2390,20 +2390,20 @@
       <c r="D20">
         <v>40</v>
       </c>
-      <c r="E20" t="s">
-        <v>300</v>
-      </c>
-      <c r="F20" t="s">
-        <v>300</v>
-      </c>
-      <c r="G20" t="s">
-        <v>300</v>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
       </c>
       <c r="H20">
         <v>13</v>
       </c>
-      <c r="I20" t="s">
-        <v>300</v>
+      <c r="I20">
+        <v>0</v>
       </c>
       <c r="J20">
         <v>112</v>
@@ -2414,17 +2414,17 @@
       <c r="L20">
         <v>5</v>
       </c>
-      <c r="M20" t="s">
-        <v>300</v>
-      </c>
-      <c r="N20" t="s">
-        <v>300</v>
-      </c>
-      <c r="O20" t="s">
-        <v>300</v>
-      </c>
-      <c r="P20" t="s">
-        <v>300</v>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2437,14 +2437,14 @@
       <c r="D21">
         <v>33</v>
       </c>
-      <c r="E21" t="s">
-        <v>300</v>
-      </c>
-      <c r="F21" t="s">
-        <v>300</v>
-      </c>
-      <c r="G21" t="s">
-        <v>300</v>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -2461,17 +2461,17 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" t="s">
-        <v>300</v>
+      <c r="M21">
+        <v>0</v>
       </c>
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="O21" t="s">
-        <v>300</v>
-      </c>
-      <c r="P21" t="s">
-        <v>300</v>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2484,20 +2484,20 @@
       <c r="D22">
         <v>16</v>
       </c>
-      <c r="E22" t="s">
-        <v>300</v>
-      </c>
-      <c r="F22" t="s">
-        <v>300</v>
-      </c>
-      <c r="G22" t="s">
-        <v>300</v>
-      </c>
-      <c r="H22" t="s">
-        <v>300</v>
-      </c>
-      <c r="I22" t="s">
-        <v>300</v>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
       </c>
       <c r="J22">
         <v>78</v>
@@ -2508,17 +2508,17 @@
       <c r="L22">
         <v>8</v>
       </c>
-      <c r="M22" t="s">
-        <v>300</v>
-      </c>
-      <c r="N22" t="s">
-        <v>300</v>
-      </c>
-      <c r="O22" t="s">
-        <v>300</v>
-      </c>
-      <c r="P22" t="s">
-        <v>300</v>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2531,20 +2531,20 @@
       <c r="D23">
         <v>18</v>
       </c>
-      <c r="E23" t="s">
-        <v>300</v>
-      </c>
-      <c r="F23" t="s">
-        <v>300</v>
-      </c>
-      <c r="G23" t="s">
-        <v>300</v>
-      </c>
-      <c r="H23" t="s">
-        <v>300</v>
-      </c>
-      <c r="I23" t="s">
-        <v>300</v>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
       </c>
       <c r="J23">
         <v>60</v>
@@ -2555,17 +2555,17 @@
       <c r="L23">
         <v>7</v>
       </c>
-      <c r="M23" t="s">
-        <v>300</v>
-      </c>
-      <c r="N23" t="s">
-        <v>300</v>
-      </c>
-      <c r="O23" t="s">
-        <v>300</v>
-      </c>
-      <c r="P23" t="s">
-        <v>300</v>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -2578,20 +2578,20 @@
       <c r="D24">
         <v>8</v>
       </c>
-      <c r="E24" t="s">
-        <v>300</v>
-      </c>
-      <c r="F24" t="s">
-        <v>300</v>
-      </c>
-      <c r="G24" t="s">
-        <v>300</v>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
       </c>
       <c r="H24">
         <v>5</v>
       </c>
-      <c r="I24" t="s">
-        <v>300</v>
+      <c r="I24">
+        <v>0</v>
       </c>
       <c r="J24">
         <v>55</v>
@@ -2602,17 +2602,17 @@
       <c r="L24">
         <v>11</v>
       </c>
-      <c r="M24" t="s">
-        <v>300</v>
-      </c>
-      <c r="N24" t="s">
-        <v>300</v>
-      </c>
-      <c r="O24" t="s">
-        <v>300</v>
-      </c>
-      <c r="P24" t="s">
-        <v>300</v>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -2625,20 +2625,20 @@
       <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25" t="s">
-        <v>300</v>
-      </c>
-      <c r="F25" t="s">
-        <v>300</v>
-      </c>
-      <c r="G25" t="s">
-        <v>300</v>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
-      <c r="I25" t="s">
-        <v>300</v>
+      <c r="I25">
+        <v>0</v>
       </c>
       <c r="J25">
         <v>97</v>
@@ -2649,14 +2649,14 @@
       <c r="L25">
         <v>3</v>
       </c>
-      <c r="M25" t="s">
-        <v>300</v>
-      </c>
-      <c r="N25" t="s">
-        <v>300</v>
-      </c>
-      <c r="O25" t="s">
-        <v>300</v>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
       </c>
       <c r="P25">
         <v>1</v>
@@ -2760,7 +2760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>201</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>203</v>
       </c>
@@ -2788,189 +2788,894 @@
         <v>1</v>
       </c>
     </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35">
+        <v>66</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>32</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>127</v>
+      </c>
+      <c r="K35">
+        <v>1708</v>
+      </c>
+      <c r="L35">
+        <v>17</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36">
+        <v>62</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1456</v>
+      </c>
+      <c r="I36">
+        <v>14</v>
+      </c>
+      <c r="J36">
+        <v>61</v>
+      </c>
+      <c r="K36">
+        <v>431</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37">
+        <v>59</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>70</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>101</v>
+      </c>
+      <c r="K37">
+        <v>1194</v>
+      </c>
+      <c r="L37">
+        <v>6</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38">
+        <v>62</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>2005</v>
+      </c>
+      <c r="I38">
+        <v>13</v>
+      </c>
+      <c r="J38">
+        <v>33</v>
+      </c>
+      <c r="K38">
+        <v>278</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>3</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39">
+        <v>62</v>
+      </c>
+      <c r="E39">
+        <v>22</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>103</v>
+      </c>
+      <c r="K39">
+        <v>1533</v>
+      </c>
+      <c r="L39">
+        <v>10</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40">
+        <v>58</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>1412</v>
+      </c>
+      <c r="I40">
+        <v>16</v>
+      </c>
+      <c r="J40">
+        <v>52</v>
+      </c>
+      <c r="K40">
+        <v>517</v>
+      </c>
+      <c r="L40">
+        <v>4</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41">
+        <v>55</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>46</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>79</v>
+      </c>
+      <c r="K41">
+        <v>990</v>
+      </c>
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>233</v>
+      </c>
+      <c r="B42" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42">
+        <v>54</v>
+      </c>
+      <c r="E42">
+        <v>7</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>115</v>
+      </c>
+      <c r="K42">
+        <v>1263</v>
+      </c>
+      <c r="L42">
+        <v>12</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43">
+        <v>53</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>109</v>
+      </c>
+      <c r="K43">
+        <v>1204</v>
+      </c>
+      <c r="L43">
+        <v>7</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44">
+        <v>49</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>1921</v>
+      </c>
+      <c r="I44">
+        <v>16</v>
+      </c>
+      <c r="J44">
+        <v>19</v>
+      </c>
+      <c r="K44">
+        <v>193</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45">
+        <v>37</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>972</v>
+      </c>
+      <c r="I45">
+        <v>8</v>
+      </c>
+      <c r="J45">
+        <v>61</v>
+      </c>
+      <c r="K45">
+        <v>498</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>235</v>
+      </c>
+      <c r="B46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46">
+        <v>56</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1255</v>
+      </c>
+      <c r="I46">
+        <v>10</v>
+      </c>
+      <c r="J46">
+        <v>49</v>
+      </c>
+      <c r="K46">
+        <v>373</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47">
+        <v>51</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>48</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>87</v>
+      </c>
+      <c r="K47">
+        <v>1282</v>
+      </c>
+      <c r="L47">
+        <v>10</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48">
+        <v>47</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>907</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
+      </c>
+      <c r="J48">
+        <v>78</v>
+      </c>
+      <c r="K48">
+        <v>592</v>
+      </c>
+      <c r="L48">
+        <v>6</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49">
+        <v>43</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>67</v>
+      </c>
+      <c r="K49">
+        <v>1079</v>
+      </c>
+      <c r="L49">
+        <v>7</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="B50" t="s">
         <v>168</v>
       </c>
       <c r="D50">
-        <v>66</v>
-      </c>
-      <c r="E50" t="s">
-        <v>300</v>
-      </c>
-      <c r="F50" t="s">
-        <v>300</v>
-      </c>
-      <c r="G50" t="s">
-        <v>300</v>
+        <v>43</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>32</v>
-      </c>
-      <c r="I50" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="K50">
-        <v>1708</v>
+        <v>1006</v>
       </c>
       <c r="L50">
-        <v>17</v>
-      </c>
-      <c r="M50" t="s">
-        <v>300</v>
-      </c>
-      <c r="N50" t="s">
-        <v>300</v>
-      </c>
-      <c r="O50" t="s">
-        <v>300</v>
-      </c>
-      <c r="P50" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
         <v>167</v>
       </c>
       <c r="D51">
-        <v>62</v>
-      </c>
-      <c r="E51" t="s">
-        <v>300</v>
-      </c>
-      <c r="F51" t="s">
-        <v>300</v>
-      </c>
-      <c r="G51" t="s">
-        <v>300</v>
+        <v>38</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>1456</v>
+        <v>1329</v>
       </c>
       <c r="I51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J51">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="K51">
-        <v>431</v>
+        <v>342</v>
       </c>
       <c r="L51">
         <v>1</v>
       </c>
-      <c r="M51" t="s">
-        <v>300</v>
-      </c>
-      <c r="N51" t="s">
-        <v>300</v>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>1</v>
-      </c>
-      <c r="P51" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
         <v>168</v>
       </c>
       <c r="D52">
-        <v>59</v>
-      </c>
-      <c r="E52" t="s">
-        <v>300</v>
-      </c>
-      <c r="F52" t="s">
-        <v>300</v>
-      </c>
-      <c r="G52" t="s">
-        <v>300</v>
+        <v>42</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>70</v>
-      </c>
-      <c r="I52" t="s">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K52">
-        <v>1194</v>
+        <v>1271</v>
       </c>
       <c r="L52">
-        <v>6</v>
-      </c>
-      <c r="M52" t="s">
-        <v>300</v>
-      </c>
-      <c r="N52" t="s">
-        <v>300</v>
+        <v>9</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B53" t="s">
         <v>167</v>
       </c>
       <c r="D53">
-        <v>62</v>
-      </c>
-      <c r="E53" t="s">
-        <v>300</v>
-      </c>
-      <c r="F53" t="s">
-        <v>300</v>
-      </c>
-      <c r="G53" t="s">
-        <v>300</v>
+        <v>36</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>2005</v>
+        <v>1431</v>
       </c>
       <c r="I53">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J53">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K53">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="L53">
-        <v>2</v>
-      </c>
-      <c r="M53" t="s">
-        <v>300</v>
-      </c>
-      <c r="N53" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P53">
         <v>1</v>
@@ -2978,93 +3683,93 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="B54" t="s">
         <v>168</v>
       </c>
       <c r="D54">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="E54">
-        <v>22</v>
-      </c>
-      <c r="F54" t="s">
-        <v>300</v>
-      </c>
-      <c r="G54" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>3</v>
-      </c>
-      <c r="I54" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="K54">
-        <v>1533</v>
+        <v>1149</v>
       </c>
       <c r="L54">
-        <v>10</v>
-      </c>
-      <c r="M54" t="s">
-        <v>300</v>
-      </c>
-      <c r="N54" t="s">
-        <v>300</v>
-      </c>
-      <c r="O54" t="s">
-        <v>300</v>
-      </c>
-      <c r="P54" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s">
         <v>167</v>
       </c>
       <c r="D55">
-        <v>58</v>
-      </c>
-      <c r="E55" t="s">
-        <v>300</v>
-      </c>
-      <c r="F55" t="s">
-        <v>300</v>
-      </c>
-      <c r="G55" t="s">
-        <v>300</v>
+        <v>28</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>1412</v>
+        <v>1122</v>
       </c>
       <c r="I55">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J55">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K55">
-        <v>517</v>
+        <v>392</v>
       </c>
       <c r="L55">
-        <v>4</v>
-      </c>
-      <c r="M55" t="s">
-        <v>300</v>
-      </c>
-      <c r="N55" t="s">
-        <v>300</v>
-      </c>
-      <c r="O55" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
       </c>
       <c r="P55">
         <v>1</v>
@@ -3072,93 +3777,93 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D56">
-        <v>55</v>
-      </c>
-      <c r="E56" t="s">
-        <v>300</v>
-      </c>
-      <c r="F56" t="s">
-        <v>300</v>
-      </c>
-      <c r="G56" t="s">
-        <v>300</v>
+        <v>36</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>46</v>
+        <v>1299</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J56">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="K56">
-        <v>990</v>
+        <v>182</v>
       </c>
       <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
         <v>3</v>
-      </c>
-      <c r="M56" t="s">
-        <v>300</v>
-      </c>
-      <c r="N56" t="s">
-        <v>300</v>
-      </c>
-      <c r="O56" t="s">
-        <v>300</v>
-      </c>
-      <c r="P56" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>233</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D57">
+        <v>24</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>990</v>
+      </c>
+      <c r="I57">
+        <v>7</v>
+      </c>
+      <c r="J57">
         <v>54</v>
       </c>
-      <c r="E57">
-        <v>7</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>300</v>
-      </c>
-      <c r="H57">
-        <v>6</v>
-      </c>
-      <c r="I57" t="s">
-        <v>300</v>
-      </c>
-      <c r="J57">
-        <v>115</v>
-      </c>
       <c r="K57">
-        <v>1263</v>
+        <v>360</v>
       </c>
       <c r="L57">
-        <v>12</v>
-      </c>
-      <c r="M57" t="s">
-        <v>300</v>
-      </c>
-      <c r="N57" t="s">
-        <v>300</v>
-      </c>
-      <c r="O57" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>1</v>
       </c>
       <c r="P57">
         <v>1</v>
@@ -3166,140 +3871,140 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
         <v>168</v>
       </c>
       <c r="D58">
-        <v>53</v>
-      </c>
-      <c r="E58" t="s">
-        <v>300</v>
-      </c>
-      <c r="F58" t="s">
-        <v>300</v>
-      </c>
-      <c r="G58" t="s">
-        <v>300</v>
+        <v>33</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
       </c>
       <c r="H58">
         <v>2</v>
       </c>
-      <c r="I58" t="s">
-        <v>300</v>
+      <c r="I58">
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="K58">
-        <v>1204</v>
+        <v>1096</v>
       </c>
       <c r="L58">
-        <v>7</v>
-      </c>
-      <c r="M58" t="s">
-        <v>300</v>
-      </c>
-      <c r="N58" t="s">
-        <v>300</v>
+        <v>13</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>1</v>
-      </c>
-      <c r="P58" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
         <v>167</v>
       </c>
       <c r="D59">
-        <v>49</v>
-      </c>
-      <c r="E59" t="s">
-        <v>300</v>
-      </c>
-      <c r="F59" t="s">
-        <v>300</v>
-      </c>
-      <c r="G59" t="s">
-        <v>300</v>
+        <v>29</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>1921</v>
+        <v>1009</v>
       </c>
       <c r="I59">
         <v>16</v>
       </c>
       <c r="J59">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K59">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="L59">
         <v>2</v>
       </c>
-      <c r="M59" t="s">
-        <v>300</v>
-      </c>
-      <c r="N59" t="s">
-        <v>300</v>
-      </c>
-      <c r="O59" t="s">
-        <v>300</v>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
         <v>167</v>
       </c>
       <c r="D60">
-        <v>37</v>
-      </c>
-      <c r="E60" t="s">
-        <v>300</v>
-      </c>
-      <c r="F60" t="s">
-        <v>300</v>
-      </c>
-      <c r="G60" t="s">
-        <v>300</v>
+        <v>29</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>972</v>
+        <v>876</v>
       </c>
       <c r="I60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J60">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K60">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="L60">
         <v>3</v>
       </c>
-      <c r="M60" t="s">
-        <v>300</v>
-      </c>
-      <c r="N60" t="s">
-        <v>300</v>
-      </c>
-      <c r="O60" t="s">
-        <v>300</v>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>2</v>
       </c>
       <c r="P60">
         <v>2</v>
@@ -3307,469 +4012,469 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D61">
-        <v>56</v>
-      </c>
-      <c r="E61" t="s">
-        <v>300</v>
-      </c>
-      <c r="F61" t="s">
-        <v>300</v>
-      </c>
-      <c r="G61" t="s">
-        <v>300</v>
+        <v>24</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>1255</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="K61">
-        <v>373</v>
+        <v>1004</v>
       </c>
       <c r="L61">
-        <v>2</v>
-      </c>
-      <c r="M61" t="s">
-        <v>300</v>
-      </c>
-      <c r="N61" t="s">
-        <v>300</v>
-      </c>
-      <c r="O61" t="s">
-        <v>300</v>
+        <v>11</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
         <v>168</v>
       </c>
       <c r="D62">
-        <v>51</v>
-      </c>
-      <c r="E62" t="s">
-        <v>300</v>
-      </c>
-      <c r="F62" t="s">
-        <v>300</v>
-      </c>
-      <c r="G62" t="s">
-        <v>300</v>
+        <v>27</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>48</v>
-      </c>
-      <c r="I62" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="K62">
-        <v>1282</v>
+        <v>911</v>
       </c>
       <c r="L62">
         <v>10</v>
       </c>
-      <c r="M62" t="s">
-        <v>300</v>
-      </c>
-      <c r="N62" t="s">
-        <v>300</v>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>2</v>
-      </c>
-      <c r="P62" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D63">
-        <v>47</v>
-      </c>
-      <c r="E63" t="s">
-        <v>300</v>
-      </c>
-      <c r="F63" t="s">
-        <v>300</v>
-      </c>
-      <c r="G63" t="s">
-        <v>300</v>
+        <v>21</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>907</v>
+        <v>53</v>
       </c>
       <c r="I63">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K63">
-        <v>592</v>
+        <v>959</v>
       </c>
       <c r="L63">
         <v>6</v>
       </c>
-      <c r="M63" t="s">
-        <v>300</v>
-      </c>
-      <c r="N63" t="s">
-        <v>300</v>
-      </c>
-      <c r="O63" t="s">
-        <v>300</v>
-      </c>
-      <c r="P63" t="s">
-        <v>300</v>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B64" t="s">
         <v>168</v>
       </c>
       <c r="D64">
-        <v>43</v>
-      </c>
-      <c r="E64" t="s">
-        <v>300</v>
-      </c>
-      <c r="F64" t="s">
-        <v>300</v>
-      </c>
-      <c r="G64" t="s">
-        <v>300</v>
-      </c>
-      <c r="H64" t="s">
-        <v>300</v>
-      </c>
-      <c r="I64" t="s">
-        <v>300</v>
+        <v>24</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="K64">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="L64">
         <v>7</v>
       </c>
-      <c r="M64" t="s">
-        <v>300</v>
-      </c>
-      <c r="N64" t="s">
-        <v>300</v>
-      </c>
-      <c r="O64" t="s">
-        <v>300</v>
-      </c>
-      <c r="P64" t="s">
-        <v>300</v>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+      <c r="P64">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="B65" t="s">
         <v>168</v>
       </c>
       <c r="D65">
-        <v>43</v>
-      </c>
-      <c r="E65" t="s">
-        <v>300</v>
-      </c>
-      <c r="F65" t="s">
-        <v>300</v>
-      </c>
-      <c r="G65" t="s">
-        <v>300</v>
-      </c>
-      <c r="H65" t="s">
-        <v>300</v>
-      </c>
-      <c r="I65" t="s">
-        <v>300</v>
+        <v>21</v>
+      </c>
+      <c r="E65">
+        <v>35</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>26</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="K65">
-        <v>1006</v>
+        <v>1130</v>
       </c>
       <c r="L65">
-        <v>7</v>
-      </c>
-      <c r="M65" t="s">
-        <v>300</v>
-      </c>
-      <c r="N65" t="s">
-        <v>300</v>
-      </c>
-      <c r="O65" t="s">
-        <v>300</v>
-      </c>
-      <c r="P65" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
         <v>167</v>
       </c>
       <c r="D66">
-        <v>38</v>
-      </c>
-      <c r="E66" t="s">
-        <v>300</v>
-      </c>
-      <c r="F66" t="s">
-        <v>300</v>
-      </c>
-      <c r="G66" t="s">
-        <v>300</v>
+        <v>20</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>1329</v>
+        <v>573</v>
       </c>
       <c r="I66">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J66">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="K66">
-        <v>342</v>
+        <v>299</v>
       </c>
       <c r="L66">
         <v>1</v>
       </c>
-      <c r="M66" t="s">
-        <v>300</v>
-      </c>
-      <c r="N66" t="s">
-        <v>300</v>
-      </c>
-      <c r="O66" t="s">
-        <v>300</v>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
         <v>168</v>
       </c>
       <c r="D67">
-        <v>42</v>
-      </c>
-      <c r="E67" t="s">
-        <v>300</v>
-      </c>
-      <c r="F67" t="s">
-        <v>300</v>
-      </c>
-      <c r="G67" t="s">
-        <v>300</v>
+        <v>17</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>-3</v>
-      </c>
-      <c r="I67" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="K67">
-        <v>1271</v>
+        <v>885</v>
       </c>
       <c r="L67">
-        <v>9</v>
-      </c>
-      <c r="M67" t="s">
-        <v>300</v>
-      </c>
-      <c r="N67" t="s">
-        <v>300</v>
-      </c>
-      <c r="O67" t="s">
-        <v>300</v>
-      </c>
-      <c r="P67" t="s">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B68" t="s">
         <v>167</v>
       </c>
       <c r="D68">
-        <v>36</v>
-      </c>
-      <c r="E68" t="s">
-        <v>300</v>
-      </c>
-      <c r="F68" t="s">
-        <v>300</v>
-      </c>
-      <c r="G68" t="s">
-        <v>300</v>
+        <v>12</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>1431</v>
+        <v>950</v>
       </c>
       <c r="I68">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="K68">
-        <v>136</v>
+        <v>543</v>
       </c>
       <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68" t="s">
-        <v>300</v>
-      </c>
-      <c r="N68" t="s">
-        <v>300</v>
-      </c>
-      <c r="O68" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>121</v>
+        <v>249</v>
       </c>
       <c r="B69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D69">
-        <v>29</v>
-      </c>
-      <c r="E69" t="s">
-        <v>300</v>
-      </c>
-      <c r="F69" t="s">
-        <v>300</v>
-      </c>
-      <c r="G69" t="s">
-        <v>300</v>
-      </c>
-      <c r="H69" t="s">
-        <v>300</v>
-      </c>
-      <c r="I69" t="s">
-        <v>300</v>
+        <v>11</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>1068</v>
+      </c>
+      <c r="I69">
+        <v>10</v>
       </c>
       <c r="J69">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K69">
-        <v>1149</v>
+        <v>281</v>
       </c>
       <c r="L69">
-        <v>7</v>
-      </c>
-      <c r="M69" t="s">
-        <v>300</v>
-      </c>
-      <c r="N69" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>1</v>
-      </c>
-      <c r="P69" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D70">
-        <v>28</v>
-      </c>
-      <c r="E70" t="s">
-        <v>300</v>
-      </c>
-      <c r="F70" t="s">
-        <v>300</v>
-      </c>
-      <c r="G70" t="s">
-        <v>300</v>
+        <v>16</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>1122</v>
+        <v>75</v>
       </c>
       <c r="I70">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="K70">
-        <v>392</v>
-      </c>
-      <c r="L70" t="s">
-        <v>300</v>
-      </c>
-      <c r="M70" t="s">
-        <v>300</v>
-      </c>
-      <c r="N70" t="s">
-        <v>300</v>
-      </c>
-      <c r="O70" t="s">
-        <v>300</v>
+        <v>966</v>
+      </c>
+      <c r="L70">
+        <v>6</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
       </c>
       <c r="P70">
         <v>1</v>
@@ -3777,140 +4482,140 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D71">
-        <v>36</v>
-      </c>
-      <c r="E71" t="s">
-        <v>300</v>
-      </c>
-      <c r="F71" t="s">
-        <v>300</v>
-      </c>
-      <c r="G71" t="s">
-        <v>300</v>
+        <v>10</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>1299</v>
+        <v>11</v>
       </c>
       <c r="I71">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="K71">
-        <v>182</v>
+        <v>831</v>
       </c>
       <c r="L71">
-        <v>2</v>
-      </c>
-      <c r="M71" t="s">
-        <v>300</v>
-      </c>
-      <c r="N71" t="s">
-        <v>300</v>
-      </c>
-      <c r="O71" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D72">
-        <v>24</v>
-      </c>
-      <c r="E72" t="s">
-        <v>300</v>
-      </c>
-      <c r="F72" t="s">
-        <v>300</v>
-      </c>
-      <c r="G72" t="s">
-        <v>300</v>
+        <v>16</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="K72">
-        <v>360</v>
+        <v>1063</v>
       </c>
       <c r="L72">
-        <v>4</v>
-      </c>
-      <c r="M72" t="s">
-        <v>300</v>
-      </c>
-      <c r="N72" t="s">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D73">
-        <v>33</v>
-      </c>
-      <c r="E73" t="s">
-        <v>300</v>
-      </c>
-      <c r="F73" t="s">
-        <v>300</v>
-      </c>
-      <c r="G73" t="s">
-        <v>300</v>
+        <v>16</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
       </c>
       <c r="H73">
+        <v>1094</v>
+      </c>
+      <c r="I73">
+        <v>8</v>
+      </c>
+      <c r="J73">
+        <v>47</v>
+      </c>
+      <c r="K73">
+        <v>414</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
         <v>2</v>
-      </c>
-      <c r="I73" t="s">
-        <v>300</v>
-      </c>
-      <c r="J73">
-        <v>82</v>
-      </c>
-      <c r="K73">
-        <v>1096</v>
-      </c>
-      <c r="L73">
-        <v>13</v>
-      </c>
-      <c r="M73" t="s">
-        <v>300</v>
-      </c>
-      <c r="N73" t="s">
-        <v>300</v>
-      </c>
-      <c r="O73" t="s">
-        <v>300</v>
       </c>
       <c r="P73">
         <v>1</v>
@@ -3918,93 +4623,93 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D74">
-        <v>29</v>
-      </c>
-      <c r="E74" t="s">
-        <v>300</v>
-      </c>
-      <c r="F74" t="s">
-        <v>300</v>
-      </c>
-      <c r="G74" t="s">
-        <v>300</v>
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>1009</v>
+        <v>61</v>
       </c>
       <c r="I74">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J74">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="K74">
-        <v>258</v>
+        <v>1001</v>
       </c>
       <c r="L74">
-        <v>2</v>
-      </c>
-      <c r="M74" t="s">
-        <v>300</v>
-      </c>
-      <c r="N74" t="s">
-        <v>300</v>
-      </c>
-      <c r="O74" t="s">
-        <v>300</v>
-      </c>
-      <c r="P74" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D75">
-        <v>29</v>
-      </c>
-      <c r="E75" t="s">
-        <v>300</v>
-      </c>
-      <c r="F75" t="s">
-        <v>300</v>
-      </c>
-      <c r="G75" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>66</v>
+      </c>
+      <c r="K75">
+        <v>992</v>
+      </c>
+      <c r="L75">
         <v>5</v>
       </c>
-      <c r="J75">
-        <v>57</v>
-      </c>
-      <c r="K75">
-        <v>483</v>
-      </c>
-      <c r="L75">
-        <v>3</v>
-      </c>
-      <c r="M75" t="s">
-        <v>300</v>
-      </c>
-      <c r="N75" t="s">
-        <v>300</v>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P75">
         <v>2</v>
@@ -4012,469 +4717,469 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D76">
-        <v>24</v>
-      </c>
-      <c r="E76" t="s">
-        <v>300</v>
-      </c>
-      <c r="F76" t="s">
-        <v>300</v>
-      </c>
-      <c r="G76" t="s">
-        <v>300</v>
-      </c>
-      <c r="H76" t="s">
-        <v>300</v>
-      </c>
-      <c r="I76" t="s">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>840</v>
+      </c>
+      <c r="I76">
+        <v>6</v>
       </c>
       <c r="J76">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="K76">
-        <v>1004</v>
+        <v>312</v>
       </c>
       <c r="L76">
-        <v>11</v>
-      </c>
-      <c r="M76" t="s">
-        <v>300</v>
-      </c>
-      <c r="N76" t="s">
-        <v>300</v>
-      </c>
-      <c r="O76" t="s">
-        <v>300</v>
-      </c>
-      <c r="P76" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D77">
-        <v>27</v>
-      </c>
-      <c r="E77" t="s">
-        <v>300</v>
-      </c>
-      <c r="F77" t="s">
-        <v>300</v>
-      </c>
-      <c r="G77" t="s">
-        <v>300</v>
-      </c>
-      <c r="H77" t="s">
-        <v>300</v>
-      </c>
-      <c r="I77" t="s">
-        <v>300</v>
+        <v>14</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>1195</v>
+      </c>
+      <c r="I77">
+        <v>10</v>
       </c>
       <c r="J77">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="K77">
-        <v>911</v>
+        <v>171</v>
       </c>
       <c r="L77">
-        <v>10</v>
-      </c>
-      <c r="M77" t="s">
-        <v>300</v>
-      </c>
-      <c r="N77" t="s">
-        <v>300</v>
-      </c>
-      <c r="O77" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>1</v>
       </c>
       <c r="P77">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="B78" t="s">
         <v>168</v>
       </c>
       <c r="D78">
-        <v>21</v>
-      </c>
-      <c r="E78" t="s">
-        <v>300</v>
-      </c>
-      <c r="F78" t="s">
-        <v>300</v>
-      </c>
-      <c r="G78" t="s">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="E78">
+        <v>30</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
       </c>
       <c r="H78">
-        <v>53</v>
-      </c>
-      <c r="I78" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
       </c>
       <c r="J78">
         <v>81</v>
       </c>
       <c r="K78">
-        <v>959</v>
+        <v>1081</v>
       </c>
       <c r="L78">
-        <v>6</v>
-      </c>
-      <c r="M78" t="s">
-        <v>300</v>
-      </c>
-      <c r="N78" t="s">
-        <v>300</v>
-      </c>
-      <c r="O78" t="s">
-        <v>300</v>
-      </c>
-      <c r="P78" t="s">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D79">
-        <v>24</v>
-      </c>
-      <c r="E79" t="s">
-        <v>300</v>
-      </c>
-      <c r="F79" t="s">
-        <v>300</v>
-      </c>
-      <c r="G79" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
       </c>
       <c r="H79">
-        <v>5</v>
-      </c>
-      <c r="I79" t="s">
-        <v>300</v>
+        <v>959</v>
+      </c>
+      <c r="I79">
+        <v>6</v>
       </c>
       <c r="J79">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="K79">
-        <v>1104</v>
+        <v>386</v>
       </c>
       <c r="L79">
-        <v>7</v>
-      </c>
-      <c r="M79" t="s">
-        <v>300</v>
-      </c>
-      <c r="N79" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>246</v>
+        <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D80">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E80">
-        <v>35</v>
-      </c>
-      <c r="F80" t="s">
-        <v>300</v>
-      </c>
-      <c r="G80" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>26</v>
-      </c>
-      <c r="I80" t="s">
-        <v>300</v>
+        <v>865</v>
+      </c>
+      <c r="I80">
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="K80">
-        <v>1130</v>
+        <v>243</v>
       </c>
       <c r="L80">
-        <v>6</v>
-      </c>
-      <c r="M80" t="s">
-        <v>300</v>
-      </c>
-      <c r="N80" t="s">
-        <v>300</v>
-      </c>
-      <c r="O80" t="s">
-        <v>300</v>
-      </c>
-      <c r="P80" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D81">
-        <v>20</v>
-      </c>
-      <c r="E81" t="s">
-        <v>300</v>
-      </c>
-      <c r="F81" t="s">
-        <v>300</v>
-      </c>
-      <c r="G81" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>573</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="K81">
-        <v>299</v>
+        <v>833</v>
       </c>
       <c r="L81">
-        <v>1</v>
-      </c>
-      <c r="M81" t="s">
-        <v>300</v>
-      </c>
-      <c r="N81" t="s">
-        <v>300</v>
-      </c>
-      <c r="O81" t="s">
-        <v>300</v>
-      </c>
-      <c r="P81" t="s">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
         <v>168</v>
       </c>
       <c r="D82">
-        <v>17</v>
-      </c>
-      <c r="E82" t="s">
-        <v>300</v>
-      </c>
-      <c r="F82" t="s">
-        <v>300</v>
-      </c>
-      <c r="G82" t="s">
-        <v>300</v>
-      </c>
-      <c r="H82" t="s">
-        <v>300</v>
-      </c>
-      <c r="I82" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>28</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
       </c>
       <c r="J82">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K82">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="L82">
-        <v>8</v>
-      </c>
-      <c r="M82" t="s">
-        <v>300</v>
-      </c>
-      <c r="N82" t="s">
-        <v>300</v>
-      </c>
-      <c r="O82" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s">
         <v>167</v>
       </c>
       <c r="D83">
-        <v>12</v>
-      </c>
-      <c r="E83" t="s">
-        <v>300</v>
-      </c>
-      <c r="F83" t="s">
-        <v>300</v>
-      </c>
-      <c r="G83" t="s">
-        <v>300</v>
+        <v>19</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>950</v>
+        <v>1016</v>
       </c>
       <c r="I83">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J83">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="K83">
-        <v>543</v>
+        <v>309</v>
       </c>
       <c r="L83">
-        <v>2</v>
-      </c>
-      <c r="M83" t="s">
-        <v>300</v>
-      </c>
-      <c r="N83" t="s">
-        <v>300</v>
-      </c>
-      <c r="O83" t="s">
-        <v>300</v>
-      </c>
-      <c r="P83" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D84">
-        <v>11</v>
-      </c>
-      <c r="E84" t="s">
-        <v>300</v>
-      </c>
-      <c r="F84" t="s">
-        <v>300</v>
-      </c>
-      <c r="G84" t="s">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>1068</v>
+        <v>55</v>
       </c>
       <c r="I84">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J84">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="K84">
-        <v>281</v>
+        <v>1017</v>
       </c>
       <c r="L84">
-        <v>1</v>
-      </c>
-      <c r="M84" t="s">
-        <v>300</v>
-      </c>
-      <c r="N84" t="s">
-        <v>300</v>
-      </c>
-      <c r="O84" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D85">
-        <v>16</v>
-      </c>
-      <c r="E85" t="s">
-        <v>300</v>
-      </c>
-      <c r="F85" t="s">
-        <v>300</v>
-      </c>
-      <c r="G85" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>75</v>
-      </c>
-      <c r="I85" t="s">
-        <v>300</v>
+        <v>775</v>
+      </c>
+      <c r="I85">
+        <v>12</v>
       </c>
       <c r="J85">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="K85">
-        <v>966</v>
+        <v>341</v>
       </c>
       <c r="L85">
-        <v>6</v>
-      </c>
-      <c r="M85" t="s">
-        <v>300</v>
-      </c>
-      <c r="N85" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85">
         <v>1</v>
@@ -4482,140 +5187,140 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B86" t="s">
         <v>168</v>
       </c>
       <c r="D86">
-        <v>10</v>
-      </c>
-      <c r="E86" t="s">
-        <v>300</v>
-      </c>
-      <c r="F86" t="s">
-        <v>300</v>
-      </c>
-      <c r="G86" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>11</v>
-      </c>
-      <c r="I86" t="s">
-        <v>300</v>
+        <v>104</v>
+      </c>
+      <c r="I86">
+        <v>3</v>
       </c>
       <c r="J86">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="K86">
-        <v>831</v>
+        <v>638</v>
       </c>
       <c r="L86">
-        <v>7</v>
-      </c>
-      <c r="M86" t="s">
-        <v>300</v>
-      </c>
-      <c r="N86" t="s">
-        <v>300</v>
-      </c>
-      <c r="O86" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D87">
-        <v>16</v>
-      </c>
-      <c r="E87" t="s">
-        <v>300</v>
-      </c>
-      <c r="F87" t="s">
-        <v>300</v>
-      </c>
-      <c r="G87" t="s">
-        <v>300</v>
-      </c>
-      <c r="H87" t="s">
-        <v>300</v>
-      </c>
-      <c r="I87" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>770</v>
+      </c>
+      <c r="I87">
+        <v>6</v>
       </c>
       <c r="J87">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="K87">
-        <v>1063</v>
+        <v>315</v>
       </c>
       <c r="L87">
-        <v>8</v>
-      </c>
-      <c r="M87" t="s">
-        <v>300</v>
-      </c>
-      <c r="N87" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>1</v>
-      </c>
-      <c r="P87" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D88">
-        <v>16</v>
-      </c>
-      <c r="E88" t="s">
-        <v>300</v>
-      </c>
-      <c r="F88" t="s">
-        <v>300</v>
-      </c>
-      <c r="G88" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>1094</v>
+        <v>28</v>
       </c>
       <c r="I88">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J88">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="K88">
-        <v>414</v>
+        <v>1032</v>
       </c>
       <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88" t="s">
-        <v>300</v>
-      </c>
-      <c r="N88" t="s">
-        <v>300</v>
+        <v>7</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P88">
         <v>1</v>
@@ -4623,516 +5328,516 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="B89" t="s">
         <v>168</v>
       </c>
       <c r="D89">
-        <v>12</v>
-      </c>
-      <c r="E89" t="s">
-        <v>300</v>
-      </c>
-      <c r="F89" t="s">
-        <v>300</v>
-      </c>
-      <c r="G89" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K89">
-        <v>1001</v>
+        <v>1059</v>
       </c>
       <c r="L89">
-        <v>7</v>
-      </c>
-      <c r="M89" t="s">
-        <v>300</v>
-      </c>
-      <c r="N89" t="s">
-        <v>300</v>
-      </c>
-      <c r="O89" t="s">
-        <v>300</v>
-      </c>
-      <c r="P89" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
         <v>168</v>
       </c>
       <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
         <v>6</v>
       </c>
-      <c r="E90" t="s">
-        <v>300</v>
-      </c>
-      <c r="F90" t="s">
-        <v>300</v>
-      </c>
-      <c r="G90" t="s">
-        <v>300</v>
-      </c>
-      <c r="H90" t="s">
-        <v>300</v>
-      </c>
-      <c r="I90" t="s">
-        <v>300</v>
+      <c r="I90">
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="K90">
-        <v>992</v>
+        <v>900</v>
       </c>
       <c r="L90">
-        <v>5</v>
-      </c>
-      <c r="M90" t="s">
-        <v>300</v>
-      </c>
-      <c r="N90" t="s">
-        <v>300</v>
-      </c>
-      <c r="O90" t="s">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>251</v>
+        <v>88</v>
       </c>
       <c r="B91" t="s">
         <v>167</v>
       </c>
       <c r="D91">
-        <v>8</v>
-      </c>
-      <c r="E91" t="s">
-        <v>300</v>
-      </c>
-      <c r="F91" t="s">
-        <v>300</v>
-      </c>
-      <c r="G91" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>840</v>
+        <v>1138</v>
       </c>
       <c r="I91">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J91">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K91">
-        <v>312</v>
+        <v>408</v>
       </c>
       <c r="L91">
         <v>2</v>
       </c>
-      <c r="M91" t="s">
-        <v>300</v>
-      </c>
-      <c r="N91" t="s">
-        <v>300</v>
-      </c>
-      <c r="O91" t="s">
-        <v>300</v>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B92" t="s">
         <v>167</v>
       </c>
       <c r="D92">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s">
-        <v>300</v>
-      </c>
-      <c r="F92" t="s">
-        <v>300</v>
-      </c>
-      <c r="G92" t="s">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>1195</v>
+        <v>1079</v>
       </c>
       <c r="I92">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J92">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K92">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="L92">
-        <v>1</v>
-      </c>
-      <c r="M92" t="s">
-        <v>300</v>
-      </c>
-      <c r="N92" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
       </c>
       <c r="O92">
         <v>1</v>
       </c>
       <c r="P92">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="B93" t="s">
         <v>168</v>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E93">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>1</v>
-      </c>
-      <c r="G93" t="s">
-        <v>300</v>
-      </c>
-      <c r="H93" t="s">
-        <v>300</v>
-      </c>
-      <c r="I93" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>12</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
       </c>
       <c r="J93">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="K93">
-        <v>1081</v>
+        <v>744</v>
       </c>
       <c r="L93">
-        <v>8</v>
-      </c>
-      <c r="M93" t="s">
-        <v>300</v>
-      </c>
-      <c r="N93" t="s">
-        <v>300</v>
-      </c>
-      <c r="O93" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>2</v>
       </c>
       <c r="P93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D94">
-        <v>7</v>
-      </c>
-      <c r="E94" t="s">
-        <v>300</v>
-      </c>
-      <c r="F94" t="s">
-        <v>300</v>
-      </c>
-      <c r="G94" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>959</v>
+        <v>15</v>
       </c>
       <c r="I94">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J94">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K94">
-        <v>386</v>
-      </c>
-      <c r="L94" t="s">
-        <v>300</v>
-      </c>
-      <c r="M94" t="s">
-        <v>300</v>
-      </c>
-      <c r="N94" t="s">
-        <v>300</v>
+        <v>734</v>
+      </c>
+      <c r="L94">
+        <v>3</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>1</v>
-      </c>
-      <c r="P94" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D95">
-        <v>7</v>
-      </c>
-      <c r="E95" t="s">
-        <v>300</v>
-      </c>
-      <c r="F95" t="s">
-        <v>300</v>
-      </c>
-      <c r="G95" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>865</v>
+        <v>20</v>
       </c>
       <c r="I95">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J95">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K95">
-        <v>243</v>
+        <v>875</v>
       </c>
       <c r="L95">
-        <v>1</v>
-      </c>
-      <c r="M95" t="s">
-        <v>300</v>
-      </c>
-      <c r="N95" t="s">
-        <v>300</v>
-      </c>
-      <c r="O95" t="s">
-        <v>300</v>
+        <v>9</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
         <v>168</v>
       </c>
       <c r="D96">
-        <v>7</v>
-      </c>
-      <c r="E96" t="s">
-        <v>300</v>
-      </c>
-      <c r="F96" t="s">
-        <v>300</v>
-      </c>
-      <c r="G96" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>1</v>
-      </c>
-      <c r="I96" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
       </c>
       <c r="J96">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="K96">
-        <v>833</v>
+        <v>1229</v>
       </c>
       <c r="L96">
-        <v>8</v>
-      </c>
-      <c r="M96" t="s">
-        <v>300</v>
-      </c>
-      <c r="N96" t="s">
-        <v>300</v>
-      </c>
-      <c r="O96" t="s">
-        <v>300</v>
-      </c>
-      <c r="P96" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>2</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="B97" t="s">
         <v>168</v>
       </c>
       <c r="D97">
-        <v>7</v>
-      </c>
-      <c r="E97" t="s">
-        <v>300</v>
-      </c>
-      <c r="F97" t="s">
-        <v>300</v>
-      </c>
-      <c r="G97" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>28</v>
-      </c>
-      <c r="I97" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
       </c>
       <c r="J97">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K97">
-        <v>899</v>
+        <v>821</v>
       </c>
       <c r="L97">
-        <v>6</v>
-      </c>
-      <c r="M97" t="s">
-        <v>300</v>
-      </c>
-      <c r="N97" t="s">
-        <v>300</v>
-      </c>
-      <c r="O97" t="s">
-        <v>300</v>
-      </c>
-      <c r="P97" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="B98" t="s">
         <v>167</v>
       </c>
       <c r="D98">
-        <v>19</v>
-      </c>
-      <c r="E98" t="s">
-        <v>300</v>
-      </c>
-      <c r="F98" t="s">
-        <v>300</v>
-      </c>
-      <c r="G98" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>1016</v>
+        <v>799</v>
       </c>
       <c r="I98">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J98">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K98">
-        <v>309</v>
+        <v>159</v>
       </c>
       <c r="L98">
-        <v>1</v>
-      </c>
-      <c r="M98" t="s">
-        <v>300</v>
-      </c>
-      <c r="N98" t="s">
-        <v>300</v>
-      </c>
-      <c r="O98" t="s">
-        <v>300</v>
-      </c>
-      <c r="P98" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D99">
-        <v>5</v>
-      </c>
-      <c r="E99" t="s">
-        <v>300</v>
-      </c>
-      <c r="F99" t="s">
-        <v>300</v>
-      </c>
-      <c r="G99" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>55</v>
+        <v>511</v>
       </c>
       <c r="I99">
         <v>1</v>
       </c>
       <c r="J99">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="K99">
-        <v>1017</v>
+        <v>310</v>
       </c>
       <c r="L99">
-        <v>4</v>
-      </c>
-      <c r="M99" t="s">
-        <v>300</v>
-      </c>
-      <c r="N99" t="s">
-        <v>300</v>
-      </c>
-      <c r="O99" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
       </c>
       <c r="P99">
         <v>1</v>
@@ -5140,281 +5845,281 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>10</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>67</v>
+      </c>
+      <c r="K100">
+        <v>710</v>
+      </c>
+      <c r="L100">
         <v>6</v>
       </c>
-      <c r="E100">
-        <v>3</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100" t="s">
-        <v>300</v>
-      </c>
-      <c r="H100">
-        <v>775</v>
-      </c>
-      <c r="I100">
-        <v>12</v>
-      </c>
-      <c r="J100">
-        <v>36</v>
-      </c>
-      <c r="K100">
-        <v>341</v>
-      </c>
-      <c r="L100" t="s">
-        <v>300</v>
-      </c>
-      <c r="M100" t="s">
-        <v>300</v>
-      </c>
-      <c r="N100" t="s">
-        <v>300</v>
-      </c>
-      <c r="O100" t="s">
-        <v>300</v>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>266</v>
       </c>
       <c r="B101" t="s">
         <v>168</v>
       </c>
       <c r="D101">
-        <v>4</v>
-      </c>
-      <c r="E101" t="s">
-        <v>300</v>
-      </c>
-      <c r="F101" t="s">
-        <v>300</v>
-      </c>
-      <c r="G101" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J101">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K101">
-        <v>638</v>
+        <v>975</v>
       </c>
       <c r="L101">
         <v>6</v>
       </c>
-      <c r="M101" t="s">
-        <v>300</v>
-      </c>
-      <c r="N101" t="s">
-        <v>300</v>
-      </c>
-      <c r="O101" t="s">
-        <v>300</v>
-      </c>
-      <c r="P101" t="s">
-        <v>300</v>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>256</v>
+        <v>97</v>
       </c>
       <c r="B102" t="s">
         <v>167</v>
       </c>
       <c r="D102">
-        <v>7</v>
-      </c>
-      <c r="E102" t="s">
-        <v>300</v>
-      </c>
-      <c r="F102" t="s">
-        <v>300</v>
-      </c>
-      <c r="G102" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>770</v>
+        <v>1043</v>
       </c>
       <c r="I102">
         <v>6</v>
       </c>
       <c r="J102">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K102">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="L102">
-        <v>2</v>
-      </c>
-      <c r="M102" t="s">
-        <v>300</v>
-      </c>
-      <c r="N102" t="s">
-        <v>300</v>
-      </c>
-      <c r="O102" t="s">
-        <v>300</v>
-      </c>
-      <c r="P102" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="B103" t="s">
         <v>168</v>
       </c>
       <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>23</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>87</v>
+      </c>
+      <c r="K103">
+        <v>1027</v>
+      </c>
+      <c r="L103">
         <v>4</v>
       </c>
-      <c r="E103" t="s">
-        <v>300</v>
-      </c>
-      <c r="F103" t="s">
-        <v>300</v>
-      </c>
-      <c r="G103" t="s">
-        <v>300</v>
-      </c>
-      <c r="H103">
-        <v>28</v>
-      </c>
-      <c r="I103" t="s">
-        <v>300</v>
-      </c>
-      <c r="J103">
-        <v>83</v>
-      </c>
-      <c r="K103">
-        <v>1032</v>
-      </c>
-      <c r="L103">
-        <v>7</v>
-      </c>
-      <c r="M103" t="s">
-        <v>300</v>
-      </c>
-      <c r="N103" t="s">
-        <v>300</v>
-      </c>
-      <c r="O103" t="s">
-        <v>300</v>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>1</v>
       </c>
       <c r="P103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D104">
-        <v>6</v>
-      </c>
-      <c r="E104" t="s">
-        <v>300</v>
-      </c>
-      <c r="F104" t="s">
-        <v>300</v>
-      </c>
-      <c r="G104" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
       </c>
       <c r="H104">
-        <v>56</v>
-      </c>
-      <c r="I104" t="s">
-        <v>300</v>
+        <v>558</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
       </c>
       <c r="J104">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="K104">
-        <v>1059</v>
+        <v>254</v>
       </c>
       <c r="L104">
-        <v>4</v>
-      </c>
-      <c r="M104" t="s">
-        <v>300</v>
-      </c>
-      <c r="N104" t="s">
-        <v>300</v>
-      </c>
-      <c r="O104" t="s">
-        <v>300</v>
-      </c>
-      <c r="P104" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>90</v>
+        <v>269</v>
       </c>
       <c r="B105" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>789</v>
+      </c>
+      <c r="I105">
         <v>3</v>
       </c>
-      <c r="E105" t="s">
-        <v>300</v>
-      </c>
-      <c r="F105" t="s">
-        <v>300</v>
-      </c>
-      <c r="G105" t="s">
-        <v>300</v>
-      </c>
-      <c r="H105">
-        <v>-6</v>
-      </c>
-      <c r="I105" t="s">
-        <v>300</v>
-      </c>
       <c r="J105">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="K105">
-        <v>900</v>
+        <v>91</v>
       </c>
       <c r="L105">
-        <v>3</v>
-      </c>
-      <c r="M105" t="s">
-        <v>300</v>
-      </c>
-      <c r="N105" t="s">
-        <v>300</v>
-      </c>
-      <c r="O105" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
       </c>
       <c r="P105">
         <v>1</v>
@@ -5422,46 +6127,46 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B106" t="s">
         <v>167</v>
       </c>
       <c r="D106">
-        <v>4</v>
-      </c>
-      <c r="E106" t="s">
-        <v>300</v>
-      </c>
-      <c r="F106" t="s">
-        <v>300</v>
-      </c>
-      <c r="G106" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
       </c>
       <c r="H106">
-        <v>1138</v>
+        <v>801</v>
       </c>
       <c r="I106">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J106">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K106">
-        <v>408</v>
+        <v>168</v>
       </c>
       <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
         <v>2</v>
-      </c>
-      <c r="M106" t="s">
-        <v>300</v>
-      </c>
-      <c r="N106" t="s">
-        <v>300</v>
-      </c>
-      <c r="O106" t="s">
-        <v>300</v>
       </c>
       <c r="P106">
         <v>3</v>
@@ -5469,430 +6174,430 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D107">
-        <v>3</v>
-      </c>
-      <c r="E107" t="s">
-        <v>300</v>
-      </c>
-      <c r="F107" t="s">
-        <v>300</v>
-      </c>
-      <c r="G107" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>1079</v>
+        <v>163</v>
       </c>
       <c r="I107">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J107">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K107">
-        <v>238</v>
-      </c>
-      <c r="L107" t="s">
-        <v>300</v>
-      </c>
-      <c r="M107" t="s">
-        <v>300</v>
-      </c>
-      <c r="N107" t="s">
-        <v>300</v>
+        <v>857</v>
+      </c>
+      <c r="L107">
+        <v>6</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="B108" t="s">
         <v>168</v>
       </c>
       <c r="D108">
-        <v>2</v>
-      </c>
-      <c r="E108" t="s">
-        <v>300</v>
-      </c>
-      <c r="F108" t="s">
-        <v>300</v>
-      </c>
-      <c r="G108" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
       </c>
       <c r="H108">
         <v>12</v>
       </c>
-      <c r="I108" t="s">
-        <v>300</v>
+      <c r="I108">
+        <v>0</v>
       </c>
       <c r="J108">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="K108">
-        <v>744</v>
+        <v>803</v>
       </c>
       <c r="L108">
-        <v>2</v>
-      </c>
-      <c r="M108" t="s">
-        <v>300</v>
-      </c>
-      <c r="N108" t="s">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>2</v>
-      </c>
-      <c r="P108" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D109">
-        <v>2</v>
-      </c>
-      <c r="E109" t="s">
-        <v>300</v>
-      </c>
-      <c r="F109" t="s">
-        <v>300</v>
-      </c>
-      <c r="G109" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>15</v>
-      </c>
-      <c r="I109" t="s">
-        <v>300</v>
+        <v>367</v>
+      </c>
+      <c r="I109">
+        <v>4</v>
       </c>
       <c r="J109">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="K109">
-        <v>734</v>
+        <v>366</v>
       </c>
       <c r="L109">
-        <v>3</v>
-      </c>
-      <c r="M109" t="s">
-        <v>300</v>
-      </c>
-      <c r="N109" t="s">
-        <v>300</v>
-      </c>
-      <c r="O109" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="B110" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D110">
-        <v>2</v>
-      </c>
-      <c r="E110" t="s">
-        <v>300</v>
-      </c>
-      <c r="F110" t="s">
-        <v>300</v>
-      </c>
-      <c r="G110" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>20</v>
+        <v>613</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J110">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="K110">
-        <v>875</v>
+        <v>393</v>
       </c>
       <c r="L110">
-        <v>9</v>
-      </c>
-      <c r="M110" t="s">
-        <v>300</v>
-      </c>
-      <c r="N110" t="s">
-        <v>300</v>
-      </c>
-      <c r="O110" t="s">
-        <v>300</v>
-      </c>
-      <c r="P110" t="s">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D111">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>513</v>
+      </c>
+      <c r="I111">
+        <v>4</v>
+      </c>
+      <c r="J111">
+        <v>52</v>
+      </c>
+      <c r="K111">
+        <v>346</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
         <v>2</v>
-      </c>
-      <c r="E111" t="s">
-        <v>300</v>
-      </c>
-      <c r="F111" t="s">
-        <v>300</v>
-      </c>
-      <c r="G111" t="s">
-        <v>300</v>
-      </c>
-      <c r="H111" t="s">
-        <v>300</v>
-      </c>
-      <c r="I111" t="s">
-        <v>300</v>
-      </c>
-      <c r="J111">
-        <v>90</v>
-      </c>
-      <c r="K111">
-        <v>1229</v>
-      </c>
-      <c r="L111">
-        <v>4</v>
-      </c>
-      <c r="M111" t="s">
-        <v>300</v>
-      </c>
-      <c r="N111" t="s">
-        <v>300</v>
-      </c>
-      <c r="O111">
-        <v>2</v>
-      </c>
-      <c r="P111" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B112" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
-      <c r="E112" t="s">
-        <v>300</v>
-      </c>
-      <c r="F112" t="s">
-        <v>300</v>
-      </c>
-      <c r="G112" t="s">
-        <v>300</v>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>4</v>
-      </c>
-      <c r="I112" t="s">
-        <v>300</v>
+        <v>569</v>
+      </c>
+      <c r="I112">
+        <v>8</v>
       </c>
       <c r="J112">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="K112">
-        <v>821</v>
+        <v>340</v>
       </c>
       <c r="L112">
-        <v>4</v>
-      </c>
-      <c r="M112" t="s">
-        <v>300</v>
-      </c>
-      <c r="N112" t="s">
-        <v>300</v>
-      </c>
-      <c r="O112" t="s">
-        <v>300</v>
-      </c>
-      <c r="P112" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D113">
         <v>2</v>
       </c>
-      <c r="E113" t="s">
-        <v>300</v>
-      </c>
-      <c r="F113" t="s">
-        <v>300</v>
-      </c>
-      <c r="G113" t="s">
-        <v>300</v>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>799</v>
+        <v>0</v>
       </c>
       <c r="I113">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J113">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="K113">
-        <v>159</v>
-      </c>
-      <c r="L113" t="s">
-        <v>300</v>
-      </c>
-      <c r="M113" t="s">
-        <v>300</v>
-      </c>
-      <c r="N113" t="s">
-        <v>300</v>
-      </c>
-      <c r="O113" t="s">
-        <v>300</v>
+        <v>808</v>
+      </c>
+      <c r="L113">
+        <v>3</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B114" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D114">
-        <v>1</v>
-      </c>
-      <c r="E114" t="s">
-        <v>300</v>
-      </c>
-      <c r="F114" t="s">
-        <v>300</v>
-      </c>
-      <c r="G114" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="K114">
-        <v>310</v>
-      </c>
-      <c r="L114" t="s">
-        <v>300</v>
-      </c>
-      <c r="M114" t="s">
-        <v>300</v>
-      </c>
-      <c r="N114" t="s">
-        <v>300</v>
-      </c>
-      <c r="O114" t="s">
-        <v>300</v>
+        <v>992</v>
+      </c>
+      <c r="L114">
+        <v>5</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="B115" t="s">
         <v>168</v>
       </c>
       <c r="D115">
-        <v>2</v>
-      </c>
-      <c r="E115" t="s">
-        <v>300</v>
-      </c>
-      <c r="F115" t="s">
-        <v>300</v>
-      </c>
-      <c r="G115" t="s">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>10</v>
-      </c>
-      <c r="I115" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="K115">
-        <v>710</v>
+        <v>756</v>
       </c>
       <c r="L115">
-        <v>6</v>
-      </c>
-      <c r="M115" t="s">
-        <v>300</v>
-      </c>
-      <c r="N115" t="s">
-        <v>300</v>
-      </c>
-      <c r="O115" t="s">
-        <v>300</v>
-      </c>
-      <c r="P115" t="s">
-        <v>300</v>
+        <v>9</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>266</v>
+        <v>130</v>
       </c>
       <c r="B116" t="s">
         <v>168</v>
@@ -5900,93 +6605,93 @@
       <c r="D116">
         <v>1</v>
       </c>
-      <c r="E116" t="s">
-        <v>300</v>
-      </c>
-      <c r="F116" t="s">
-        <v>300</v>
-      </c>
-      <c r="G116" t="s">
-        <v>300</v>
-      </c>
-      <c r="H116" t="s">
-        <v>300</v>
-      </c>
-      <c r="I116" t="s">
-        <v>300</v>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
       </c>
       <c r="J116">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="K116">
-        <v>975</v>
+        <v>610</v>
       </c>
       <c r="L116">
-        <v>6</v>
-      </c>
-      <c r="M116" t="s">
-        <v>300</v>
-      </c>
-      <c r="N116" t="s">
-        <v>300</v>
-      </c>
-      <c r="O116" t="s">
-        <v>300</v>
-      </c>
-      <c r="P116" t="s">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>97</v>
+        <v>279</v>
       </c>
       <c r="B117" t="s">
         <v>167</v>
       </c>
       <c r="D117">
-        <v>1</v>
-      </c>
-      <c r="E117" t="s">
-        <v>300</v>
-      </c>
-      <c r="F117" t="s">
-        <v>300</v>
-      </c>
-      <c r="G117" t="s">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>1043</v>
+        <v>728</v>
       </c>
       <c r="I117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J117">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K117">
-        <v>283</v>
-      </c>
-      <c r="L117" t="s">
-        <v>300</v>
-      </c>
-      <c r="M117" t="s">
-        <v>300</v>
-      </c>
-      <c r="N117" t="s">
-        <v>300</v>
-      </c>
-      <c r="O117" t="s">
-        <v>300</v>
-      </c>
-      <c r="P117" t="s">
-        <v>300</v>
+        <v>176</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B118" t="s">
         <v>168</v>
@@ -5994,46 +6699,46 @@
       <c r="D118">
         <v>1</v>
       </c>
-      <c r="E118" t="s">
-        <v>300</v>
-      </c>
-      <c r="F118" t="s">
-        <v>300</v>
-      </c>
-      <c r="G118" t="s">
-        <v>300</v>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>23</v>
-      </c>
-      <c r="I118" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
       </c>
       <c r="J118">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="K118">
-        <v>1027</v>
+        <v>615</v>
       </c>
       <c r="L118">
-        <v>4</v>
-      </c>
-      <c r="M118" t="s">
-        <v>300</v>
-      </c>
-      <c r="N118" t="s">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>1</v>
-      </c>
-      <c r="P118" t="s">
-        <v>300</v>
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>281</v>
       </c>
       <c r="B119" t="s">
         <v>167</v>
@@ -6041,38 +6746,38 @@
       <c r="D119">
         <v>1</v>
       </c>
-      <c r="E119" t="s">
-        <v>300</v>
-      </c>
-      <c r="F119" t="s">
-        <v>300</v>
-      </c>
-      <c r="G119" t="s">
-        <v>300</v>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>558</v>
+        <v>766</v>
       </c>
       <c r="I119">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J119">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="K119">
-        <v>254</v>
-      </c>
-      <c r="L119" t="s">
-        <v>300</v>
-      </c>
-      <c r="M119" t="s">
-        <v>300</v>
-      </c>
-      <c r="N119" t="s">
-        <v>300</v>
-      </c>
-      <c r="O119" t="s">
-        <v>300</v>
+        <v>54</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
       </c>
       <c r="P119">
         <v>1</v>
@@ -6080,7 +6785,7 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B120" t="s">
         <v>167</v>
@@ -6088,46 +6793,46 @@
       <c r="D120">
         <v>1</v>
       </c>
-      <c r="E120" t="s">
-        <v>300</v>
-      </c>
-      <c r="F120" t="s">
-        <v>300</v>
-      </c>
-      <c r="G120" t="s">
-        <v>300</v>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>789</v>
+        <v>442</v>
       </c>
       <c r="I120">
         <v>3</v>
       </c>
       <c r="J120">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K120">
-        <v>91</v>
-      </c>
-      <c r="L120" t="s">
-        <v>300</v>
-      </c>
-      <c r="M120" t="s">
-        <v>300</v>
-      </c>
-      <c r="N120" t="s">
-        <v>300</v>
-      </c>
-      <c r="O120" t="s">
-        <v>300</v>
+        <v>189</v>
+      </c>
+      <c r="L120">
+        <v>3</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="B121" t="s">
         <v>167</v>
@@ -6135,46 +6840,46 @@
       <c r="D121">
         <v>1</v>
       </c>
-      <c r="E121" t="s">
-        <v>300</v>
-      </c>
-      <c r="F121" t="s">
-        <v>300</v>
-      </c>
-      <c r="G121" t="s">
-        <v>300</v>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>801</v>
+        <v>1079</v>
       </c>
       <c r="I121">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J121">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K121">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="L121">
-        <v>1</v>
-      </c>
-      <c r="M121" t="s">
-        <v>300</v>
-      </c>
-      <c r="N121" t="s">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
       </c>
       <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
         <v>2</v>
-      </c>
-      <c r="P121">
-        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="B122" t="s">
         <v>168</v>
@@ -6182,797 +6887,92 @@
       <c r="D122">
         <v>1</v>
       </c>
-      <c r="E122" t="s">
-        <v>300</v>
-      </c>
-      <c r="F122" t="s">
-        <v>300</v>
-      </c>
-      <c r="G122" t="s">
-        <v>300</v>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="I122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="K122">
-        <v>857</v>
+        <v>601</v>
       </c>
       <c r="L122">
-        <v>6</v>
-      </c>
-      <c r="M122" t="s">
-        <v>300</v>
-      </c>
-      <c r="N122" t="s">
-        <v>300</v>
-      </c>
-      <c r="O122" t="s">
-        <v>300</v>
+        <v>4</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>1</v>
       </c>
       <c r="P122">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B123" t="s">
         <v>168</v>
       </c>
       <c r="D123">
-        <v>1</v>
-      </c>
-      <c r="E123" t="s">
-        <v>300</v>
-      </c>
-      <c r="F123" t="s">
-        <v>300</v>
-      </c>
-      <c r="G123" t="s">
-        <v>300</v>
+        <v>3</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>12</v>
-      </c>
-      <c r="I123" t="s">
-        <v>300</v>
+        <v>43</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
       </c>
       <c r="J123">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="K123">
-        <v>803</v>
+        <v>461</v>
       </c>
       <c r="L123">
-        <v>5</v>
-      </c>
-      <c r="M123" t="s">
-        <v>300</v>
-      </c>
-      <c r="N123" t="s">
-        <v>300</v>
-      </c>
-      <c r="O123" t="s">
-        <v>300</v>
-      </c>
-      <c r="P123" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124" t="s">
-        <v>167</v>
-      </c>
-      <c r="D124">
-        <v>1</v>
-      </c>
-      <c r="E124" t="s">
-        <v>300</v>
-      </c>
-      <c r="F124" t="s">
-        <v>300</v>
-      </c>
-      <c r="G124" t="s">
-        <v>300</v>
-      </c>
-      <c r="H124">
-        <v>367</v>
-      </c>
-      <c r="I124">
-        <v>4</v>
-      </c>
-      <c r="J124">
-        <v>35</v>
-      </c>
-      <c r="K124">
-        <v>366</v>
-      </c>
-      <c r="L124" t="s">
-        <v>300</v>
-      </c>
-      <c r="M124" t="s">
-        <v>300</v>
-      </c>
-      <c r="N124" t="s">
-        <v>300</v>
-      </c>
-      <c r="O124" t="s">
-        <v>300</v>
-      </c>
-      <c r="P124" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>72</v>
-      </c>
-      <c r="B125" t="s">
-        <v>167</v>
-      </c>
-      <c r="D125">
-        <v>1</v>
-      </c>
-      <c r="E125" t="s">
-        <v>300</v>
-      </c>
-      <c r="F125" t="s">
-        <v>300</v>
-      </c>
-      <c r="G125" t="s">
-        <v>300</v>
-      </c>
-      <c r="H125">
-        <v>613</v>
-      </c>
-      <c r="I125">
-        <v>3</v>
-      </c>
-      <c r="J125">
-        <v>51</v>
-      </c>
-      <c r="K125">
-        <v>393</v>
-      </c>
-      <c r="L125">
-        <v>6</v>
-      </c>
-      <c r="M125" t="s">
-        <v>300</v>
-      </c>
-      <c r="N125" t="s">
-        <v>300</v>
-      </c>
-      <c r="O125" t="s">
-        <v>300</v>
-      </c>
-      <c r="P125">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>111</v>
-      </c>
-      <c r="B126" t="s">
-        <v>167</v>
-      </c>
-      <c r="D126">
-        <v>1</v>
-      </c>
-      <c r="E126" t="s">
-        <v>300</v>
-      </c>
-      <c r="F126" t="s">
-        <v>300</v>
-      </c>
-      <c r="G126" t="s">
-        <v>300</v>
-      </c>
-      <c r="H126">
-        <v>513</v>
-      </c>
-      <c r="I126">
-        <v>4</v>
-      </c>
-      <c r="J126">
-        <v>52</v>
-      </c>
-      <c r="K126">
-        <v>346</v>
-      </c>
-      <c r="L126" t="s">
-        <v>300</v>
-      </c>
-      <c r="M126" t="s">
-        <v>300</v>
-      </c>
-      <c r="N126" t="s">
-        <v>300</v>
-      </c>
-      <c r="O126" t="s">
-        <v>300</v>
-      </c>
-      <c r="P126">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>143</v>
-      </c>
-      <c r="B127" t="s">
-        <v>167</v>
-      </c>
-      <c r="D127">
-        <v>1</v>
-      </c>
-      <c r="E127" t="s">
-        <v>300</v>
-      </c>
-      <c r="F127" t="s">
-        <v>300</v>
-      </c>
-      <c r="G127" t="s">
-        <v>300</v>
-      </c>
-      <c r="H127">
-        <v>569</v>
-      </c>
-      <c r="I127">
         <v>8</v>
       </c>
-      <c r="J127">
-        <v>42</v>
-      </c>
-      <c r="K127">
-        <v>340</v>
-      </c>
-      <c r="L127">
-        <v>1</v>
-      </c>
-      <c r="M127" t="s">
-        <v>300</v>
-      </c>
-      <c r="N127" t="s">
-        <v>300</v>
-      </c>
-      <c r="O127" t="s">
-        <v>300</v>
-      </c>
-      <c r="P127" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>99</v>
-      </c>
-      <c r="B128" t="s">
-        <v>168</v>
-      </c>
-      <c r="D128">
-        <v>2</v>
-      </c>
-      <c r="E128" t="s">
-        <v>300</v>
-      </c>
-      <c r="F128" t="s">
-        <v>300</v>
-      </c>
-      <c r="G128" t="s">
-        <v>300</v>
-      </c>
-      <c r="H128" t="s">
-        <v>300</v>
-      </c>
-      <c r="I128" t="s">
-        <v>300</v>
-      </c>
-      <c r="J128">
-        <v>69</v>
-      </c>
-      <c r="K128">
-        <v>808</v>
-      </c>
-      <c r="L128">
-        <v>3</v>
-      </c>
-      <c r="M128" t="s">
-        <v>300</v>
-      </c>
-      <c r="N128" t="s">
-        <v>300</v>
-      </c>
-      <c r="O128" t="s">
-        <v>300</v>
-      </c>
-      <c r="P128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>147</v>
-      </c>
-      <c r="B129" t="s">
-        <v>168</v>
-      </c>
-      <c r="D129">
-        <v>2</v>
-      </c>
-      <c r="E129" t="s">
-        <v>300</v>
-      </c>
-      <c r="F129" t="s">
-        <v>300</v>
-      </c>
-      <c r="G129" t="s">
-        <v>300</v>
-      </c>
-      <c r="H129" t="s">
-        <v>300</v>
-      </c>
-      <c r="I129" t="s">
-        <v>300</v>
-      </c>
-      <c r="J129">
-        <v>64</v>
-      </c>
-      <c r="K129">
-        <v>992</v>
-      </c>
-      <c r="L129">
-        <v>5</v>
-      </c>
-      <c r="M129" t="s">
-        <v>300</v>
-      </c>
-      <c r="N129" t="s">
-        <v>300</v>
-      </c>
-      <c r="O129" t="s">
-        <v>300</v>
-      </c>
-      <c r="P129" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>159</v>
-      </c>
-      <c r="B130" t="s">
-        <v>168</v>
-      </c>
-      <c r="D130">
-        <v>1</v>
-      </c>
-      <c r="E130" t="s">
-        <v>300</v>
-      </c>
-      <c r="F130" t="s">
-        <v>300</v>
-      </c>
-      <c r="G130" t="s">
-        <v>300</v>
-      </c>
-      <c r="H130" t="s">
-        <v>300</v>
-      </c>
-      <c r="I130" t="s">
-        <v>300</v>
-      </c>
-      <c r="J130">
-        <v>45</v>
-      </c>
-      <c r="K130">
-        <v>756</v>
-      </c>
-      <c r="L130">
-        <v>9</v>
-      </c>
-      <c r="M130" t="s">
-        <v>300</v>
-      </c>
-      <c r="N130" t="s">
-        <v>300</v>
-      </c>
-      <c r="O130" t="s">
-        <v>300</v>
-      </c>
-      <c r="P130" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>130</v>
-      </c>
-      <c r="B131" t="s">
-        <v>168</v>
-      </c>
-      <c r="D131">
-        <v>1</v>
-      </c>
-      <c r="E131" t="s">
-        <v>300</v>
-      </c>
-      <c r="F131" t="s">
-        <v>300</v>
-      </c>
-      <c r="G131" t="s">
-        <v>300</v>
-      </c>
-      <c r="H131" t="s">
-        <v>300</v>
-      </c>
-      <c r="I131" t="s">
-        <v>300</v>
-      </c>
-      <c r="J131">
-        <v>56</v>
-      </c>
-      <c r="K131">
-        <v>610</v>
-      </c>
-      <c r="L131">
-        <v>5</v>
-      </c>
-      <c r="M131" t="s">
-        <v>300</v>
-      </c>
-      <c r="N131" t="s">
-        <v>300</v>
-      </c>
-      <c r="O131" t="s">
-        <v>300</v>
-      </c>
-      <c r="P131" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>279</v>
-      </c>
-      <c r="B132" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132">
-        <v>2</v>
-      </c>
-      <c r="E132" t="s">
-        <v>300</v>
-      </c>
-      <c r="F132" t="s">
-        <v>300</v>
-      </c>
-      <c r="G132" t="s">
-        <v>300</v>
-      </c>
-      <c r="H132">
-        <v>728</v>
-      </c>
-      <c r="I132">
-        <v>7</v>
-      </c>
-      <c r="J132">
-        <v>23</v>
-      </c>
-      <c r="K132">
-        <v>176</v>
-      </c>
-      <c r="L132" t="s">
-        <v>300</v>
-      </c>
-      <c r="M132" t="s">
-        <v>300</v>
-      </c>
-      <c r="N132" t="s">
-        <v>300</v>
-      </c>
-      <c r="O132" t="s">
-        <v>300</v>
-      </c>
-      <c r="P132" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>141</v>
-      </c>
-      <c r="B133" t="s">
-        <v>168</v>
-      </c>
-      <c r="D133">
-        <v>1</v>
-      </c>
-      <c r="E133" t="s">
-        <v>300</v>
-      </c>
-      <c r="F133" t="s">
-        <v>300</v>
-      </c>
-      <c r="G133" t="s">
-        <v>300</v>
-      </c>
-      <c r="H133" t="s">
-        <v>300</v>
-      </c>
-      <c r="I133" t="s">
-        <v>300</v>
-      </c>
-      <c r="J133">
-        <v>48</v>
-      </c>
-      <c r="K133">
-        <v>615</v>
-      </c>
-      <c r="L133">
-        <v>5</v>
-      </c>
-      <c r="M133" t="s">
-        <v>300</v>
-      </c>
-      <c r="N133" t="s">
-        <v>300</v>
-      </c>
-      <c r="O133" t="s">
-        <v>300</v>
-      </c>
-      <c r="P133" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>281</v>
-      </c>
-      <c r="B134" t="s">
-        <v>167</v>
-      </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134" t="s">
-        <v>300</v>
-      </c>
-      <c r="F134" t="s">
-        <v>300</v>
-      </c>
-      <c r="G134" t="s">
-        <v>300</v>
-      </c>
-      <c r="H134">
-        <v>766</v>
-      </c>
-      <c r="I134">
-        <v>7</v>
-      </c>
-      <c r="J134">
-        <v>7</v>
-      </c>
-      <c r="K134">
-        <v>54</v>
-      </c>
-      <c r="L134" t="s">
-        <v>300</v>
-      </c>
-      <c r="M134" t="s">
-        <v>300</v>
-      </c>
-      <c r="N134" t="s">
-        <v>300</v>
-      </c>
-      <c r="O134" t="s">
-        <v>300</v>
-      </c>
-      <c r="P134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>283</v>
-      </c>
-      <c r="B135" t="s">
-        <v>167</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s">
-        <v>300</v>
-      </c>
-      <c r="F135" t="s">
-        <v>300</v>
-      </c>
-      <c r="G135" t="s">
-        <v>300</v>
-      </c>
-      <c r="H135">
-        <v>442</v>
-      </c>
-      <c r="I135">
-        <v>3</v>
-      </c>
-      <c r="J135">
-        <v>17</v>
-      </c>
-      <c r="K135">
-        <v>189</v>
-      </c>
-      <c r="L135">
-        <v>3</v>
-      </c>
-      <c r="M135" t="s">
-        <v>300</v>
-      </c>
-      <c r="N135" t="s">
-        <v>300</v>
-      </c>
-      <c r="O135" t="s">
-        <v>300</v>
-      </c>
-      <c r="P135" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>284</v>
-      </c>
-      <c r="B136" t="s">
-        <v>167</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136" t="s">
-        <v>300</v>
-      </c>
-      <c r="F136" t="s">
-        <v>300</v>
-      </c>
-      <c r="G136" t="s">
-        <v>300</v>
-      </c>
-      <c r="H136">
-        <v>1079</v>
-      </c>
-      <c r="I136">
-        <v>2</v>
-      </c>
-      <c r="J136">
-        <v>39</v>
-      </c>
-      <c r="K136">
-        <v>249</v>
-      </c>
-      <c r="L136">
-        <v>3</v>
-      </c>
-      <c r="M136" t="s">
-        <v>300</v>
-      </c>
-      <c r="N136" t="s">
-        <v>300</v>
-      </c>
-      <c r="O136" t="s">
-        <v>300</v>
-      </c>
-      <c r="P136">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>131</v>
-      </c>
-      <c r="B137" t="s">
-        <v>168</v>
-      </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137" t="s">
-        <v>300</v>
-      </c>
-      <c r="F137" t="s">
-        <v>300</v>
-      </c>
-      <c r="G137" t="s">
-        <v>300</v>
-      </c>
-      <c r="H137" t="s">
-        <v>300</v>
-      </c>
-      <c r="I137" t="s">
-        <v>300</v>
-      </c>
-      <c r="J137">
-        <v>46</v>
-      </c>
-      <c r="K137">
-        <v>601</v>
-      </c>
-      <c r="L137">
-        <v>4</v>
-      </c>
-      <c r="M137" t="s">
-        <v>300</v>
-      </c>
-      <c r="N137" t="s">
-        <v>300</v>
-      </c>
-      <c r="O137">
-        <v>1</v>
-      </c>
-      <c r="P137" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>154</v>
-      </c>
-      <c r="B138" t="s">
-        <v>168</v>
-      </c>
-      <c r="D138">
-        <v>3</v>
-      </c>
-      <c r="E138" t="s">
-        <v>300</v>
-      </c>
-      <c r="F138" t="s">
-        <v>300</v>
-      </c>
-      <c r="G138" t="s">
-        <v>300</v>
-      </c>
-      <c r="H138">
-        <v>43</v>
-      </c>
-      <c r="I138" t="s">
-        <v>300</v>
-      </c>
-      <c r="J138">
-        <v>37</v>
-      </c>
-      <c r="K138">
-        <v>461</v>
-      </c>
-      <c r="L138">
-        <v>8</v>
-      </c>
-      <c r="M138" t="s">
-        <v>300</v>
-      </c>
-      <c r="N138" t="s">
-        <v>300</v>
-      </c>
-      <c r="O138" t="s">
-        <v>300</v>
-      </c>
-      <c r="P138" t="s">
-        <v>300</v>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P138" xr:uid="{CB547F50-6C6F-4210-B1EE-78B38AE722A6}"/>
+  <autoFilter ref="A1:P123" xr:uid="{CB547F50-6C6F-4210-B1EE-78B38AE722A6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/fantasy_app.xlsx
+++ b/fantasy_app.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sleeper" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESPN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Adjustments" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -15586,4 +15587,95 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adjust %</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Commissioner Exempt List - possible suspension (as of Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Zach Charbonnet</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>On PUP list - injury</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Recovering from torn Achilles - Week 1 status uncertain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rashod Bateman</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arrested (family violence) - possible suspension</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/fantasy_app.xlsx
+++ b/fantasy_app.xlsx
@@ -15595,7 +15595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15648,7 +15648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>George Kittle</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -15656,22 +15656,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Recovering from torn Achilles - Week 1 status uncertain</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Rashod Bateman</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-20</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Arrested (family violence) - possible suspension</t>
+          <t>Offseason legal matter - suspension risk</t>
         </is>
       </c>
     </row>

--- a/fantasy_app.xlsx
+++ b/fantasy_app.xlsx
@@ -15595,7 +15595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Commissioner Exempt List - possible suspension (as of Sep 2026)</t>
+          <t>Injury/legal: Commissioner Exempt List - possible suspension</t>
         </is>
       </c>
     </row>
@@ -15641,14 +15641,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>On PUP list - injury</t>
+          <t>Injury: on PUP list</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -15656,7 +15656,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Offseason legal matter - suspension risk</t>
+          <t>Legal: arrested (family violence) - possible suspension</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Puka Nacua</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Legal: offseason matter - suspension risk</t>
         </is>
       </c>
     </row>
